--- a/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
+++ b/data/Capus_LHommeBicycle_1893/Capus_LHommeBicycle_1893.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\data\Capus_LHommeBicycle_1893\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44558AB3-8C7E-4D92-A2CC-3C4A2DEB92E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AD1DFD-081F-4AE2-9833-3DCBA908A229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="408">
   <si>
     <t>Classe</t>
   </si>
@@ -114,75 +114,12 @@
     <t>Kamtchatka</t>
   </si>
   <si>
-    <t>:NU01</t>
-  </si>
-  <si>
-    <t>:NU02</t>
-  </si>
-  <si>
-    <t>:NU03</t>
-  </si>
-  <si>
     <t>:Bicycle</t>
   </si>
   <si>
-    <t>:NU04</t>
-  </si>
-  <si>
-    <t>:NU05</t>
-  </si>
-  <si>
-    <t>:NU06</t>
-  </si>
-  <si>
-    <t>:NU07</t>
-  </si>
-  <si>
-    <t>:NU08</t>
-  </si>
-  <si>
-    <t>:NU09</t>
-  </si>
-  <si>
-    <t>:NU10</t>
-  </si>
-  <si>
-    <t>:NU11</t>
-  </si>
-  <si>
-    <t>:NU12</t>
-  </si>
-  <si>
-    <t>:NU13</t>
-  </si>
-  <si>
-    <t>:NU14</t>
-  </si>
-  <si>
-    <t>:NU15</t>
-  </si>
-  <si>
     <t>:NU16</t>
   </si>
   <si>
-    <t>:NU17</t>
-  </si>
-  <si>
-    <t>:NU18</t>
-  </si>
-  <si>
-    <t>:NU19</t>
-  </si>
-  <si>
-    <t>:NU20</t>
-  </si>
-  <si>
-    <t>:NU21</t>
-  </si>
-  <si>
-    <t>:NU22</t>
-  </si>
-  <si>
     <t>G3_Psychological_State</t>
   </si>
   <si>
@@ -379,9 +316,6 @@
   </si>
   <si>
     <t>Narrative Sequence</t>
-  </si>
-  <si>
-    <t>E55 Types</t>
   </si>
   <si>
     <t>G5 Narrative Event</t>
@@ -411,9 +345,6 @@
   </si>
   <si>
     <t>P67 refers to G5 Narrative Event</t>
-  </si>
-  <si>
-    <t>:NU23</t>
   </si>
   <si>
     <t>H2_Concrete_Novum</t>
@@ -1185,12 +1116,6 @@
     <t>value</t>
   </si>
   <si>
-    <t>:Sequence_Fabula</t>
-  </si>
-  <si>
-    <t>:Sequence_Syuzhet</t>
-  </si>
-  <si>
     <t>:Sequence_Medicine_fails_to_diagnose_a_disease</t>
   </si>
   <si>
@@ -1267,6 +1192,87 @@
   </si>
   <si>
     <t>H4_Non-Human_Character</t>
+  </si>
+  <si>
+    <t>novum introduced by</t>
+  </si>
+  <si>
+    <t>:Sequence_Fabula_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:Sequence_Syuzhet_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:Feature_wonderful_register</t>
+  </si>
+  <si>
+    <t>:NU01_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU02_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU03_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU04_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU05_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU06_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU07_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU08_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU09_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU10_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU11_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU12_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU13_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU14_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU15_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU16_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU17_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU18_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU19_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU20_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU21_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU22_LHomme_Bicycle</t>
+  </si>
+  <si>
+    <t>:NU23_LHomme_Bicycle</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1553,9 +1559,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1581,6 +1584,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1588,7 +1596,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1612,14 +1619,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1944,7 +1951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1954,17 +1961,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -1973,10 +1980,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1984,10 +1991,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -2001,10 +2008,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2015,7 +2022,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2026,7 +2033,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2034,21 +2041,21 @@
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
       <c r="D7" s="19" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="40" customFormat="1" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2056,10 +2063,10 @@
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="19" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2067,10 +2074,10 @@
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>75</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2078,10 +2085,10 @@
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="19" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2089,10 +2096,10 @@
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>274</v>
+        <v>203</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>379</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2100,32 +2107,32 @@
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="19" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="20" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="20" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="19"/>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="19" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2133,10 +2140,10 @@
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2144,81 +2151,92 @@
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
       <c r="D17" s="19" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="20" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="20" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="B19" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="D19" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19" t="s">
-        <v>8</v>
-      </c>
       <c r="E19" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="G19" s="56"/>
+        <v>290</v>
+      </c>
     </row>
     <row r="20" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="35">
-        <v>1983</v>
-      </c>
-      <c r="G20" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="52"/>
     </row>
     <row r="21" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
       <c r="D21" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="54">
+        <v>1893</v>
+      </c>
+      <c r="G21" s="52"/>
+    </row>
+    <row r="22" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E22" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="24"/>
-    </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="13"/>
+      <c r="B24" s="24"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="41"/>
+      <c r="B25" s="13"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="14"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="14"/>
+      <c r="B26" s="40"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="14"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="13"/>
+      <c r="B29" s="14"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2236,23 +2254,23 @@
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="24.88671875" style="52" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" style="51" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="32.21875" style="52" customWidth="1"/>
+    <col min="5" max="5" width="32.21875" style="51" customWidth="1"/>
     <col min="6" max="6" width="22" style="15" customWidth="1"/>
     <col min="7" max="7" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2264,40 +2282,40 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>115</v>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>379</v>
+        <v>31</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>382</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>26</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2306,13 +2324,13 @@
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
       <c r="E4" s="21" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>27</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2322,10 +2340,10 @@
       <c r="D5" s="19"/>
       <c r="E5" s="19"/>
       <c r="F5" s="19" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>28</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2335,10 +2353,10 @@
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
       <c r="F6" s="21" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>30</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2347,13 +2365,13 @@
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
       <c r="E7" s="32" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>31</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2362,13 +2380,13 @@
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
       <c r="E8" s="7" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>32</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2377,13 +2395,13 @@
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
       <c r="E9" s="32" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>33</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2392,13 +2410,13 @@
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
       <c r="E10" s="7" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>34</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2407,13 +2425,13 @@
       <c r="C11" s="19"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>35</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2422,13 +2440,13 @@
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>36</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2437,13 +2455,13 @@
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
       <c r="E13" s="19" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>37</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2452,13 +2470,13 @@
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
       <c r="E14" s="21" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>38</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2467,13 +2485,13 @@
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>39</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2482,13 +2500,13 @@
       <c r="C16" s="21"/>
       <c r="D16" s="21"/>
       <c r="E16" s="21" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>40</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2497,13 +2515,13 @@
       <c r="C17" s="19"/>
       <c r="D17" s="19"/>
       <c r="E17" s="32" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>41</v>
+        <v>399</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2512,13 +2530,13 @@
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
       <c r="E18" s="7" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>42</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2527,13 +2545,13 @@
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
       <c r="E19" s="32" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>43</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2542,13 +2560,13 @@
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
       <c r="E20" s="7" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>44</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2557,13 +2575,13 @@
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
       <c r="E21" s="32" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>45</v>
+        <v>403</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2572,13 +2590,13 @@
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="7" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>46</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2587,13 +2605,13 @@
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
       <c r="E23" s="32" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>47</v>
+        <v>405</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2602,13 +2620,13 @@
       <c r="C24" s="21"/>
       <c r="D24" s="21"/>
       <c r="E24" s="7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>48</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2617,36 +2635,36 @@
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
       <c r="E25" s="32" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>124</v>
+        <v>407</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>380</v>
+        <v>31</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>26</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2655,13 +2673,13 @@
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>27</v>
+        <v>386</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2671,10 +2689,10 @@
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>28</v>
+        <v>387</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2684,10 +2702,10 @@
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>30</v>
+        <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2696,13 +2714,13 @@
       <c r="C30" s="21"/>
       <c r="D30" s="21"/>
       <c r="E30" s="21" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>31</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2711,13 +2729,13 @@
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
       <c r="E31" s="19" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>32</v>
+        <v>390</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2726,13 +2744,13 @@
       <c r="C32" s="21"/>
       <c r="D32" s="21"/>
       <c r="E32" s="21" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>33</v>
+        <v>391</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2741,13 +2759,13 @@
       <c r="C33" s="19"/>
       <c r="D33" s="19"/>
       <c r="E33" s="19" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>34</v>
+        <v>392</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2756,13 +2774,13 @@
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
       <c r="E34" s="21" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>35</v>
+        <v>393</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2771,13 +2789,13 @@
       <c r="C35" s="19"/>
       <c r="D35" s="19"/>
       <c r="E35" s="19" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>36</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2786,13 +2804,13 @@
       <c r="C36" s="21"/>
       <c r="D36" s="21"/>
       <c r="E36" s="21" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>37</v>
+        <v>395</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2801,13 +2819,13 @@
       <c r="C37" s="19"/>
       <c r="D37" s="19"/>
       <c r="E37" s="19" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>38</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2816,13 +2834,13 @@
       <c r="C38" s="21"/>
       <c r="D38" s="21"/>
       <c r="E38" s="21" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>39</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2831,13 +2849,13 @@
       <c r="C39" s="19"/>
       <c r="D39" s="19"/>
       <c r="E39" s="19" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>40</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2846,13 +2864,13 @@
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>41</v>
+        <v>399</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2861,13 +2879,13 @@
       <c r="C41" s="19"/>
       <c r="D41" s="19"/>
       <c r="E41" s="19" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>42</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2876,13 +2894,13 @@
       <c r="C42" s="21"/>
       <c r="D42" s="21"/>
       <c r="E42" s="21" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>43</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2891,13 +2909,13 @@
       <c r="C43" s="19"/>
       <c r="D43" s="19"/>
       <c r="E43" s="19" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>44</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2906,13 +2924,13 @@
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
       <c r="E44" s="21" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="G44" s="21" t="s">
-        <v>45</v>
+        <v>403</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2921,13 +2939,13 @@
       <c r="C45" s="19"/>
       <c r="D45" s="19"/>
       <c r="E45" s="19" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>46</v>
+        <v>404</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2936,13 +2954,13 @@
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>47</v>
+        <v>405</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2951,13 +2969,13 @@
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>48</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -2966,34 +2984,34 @@
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="G48" s="21" t="s">
-        <v>124</v>
+        <v>246</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="20" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="32" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>39</v>
+        <v>224</v>
+      </c>
+      <c r="G49" s="32" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -3002,13 +3020,13 @@
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>40</v>
+        <v>225</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -3017,34 +3035,34 @@
       <c r="C51" s="19"/>
       <c r="D51" s="19"/>
       <c r="E51" s="32" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>41</v>
+        <v>226</v>
+      </c>
+      <c r="G51" s="32" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="21" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="G52" s="21" t="s">
-        <v>35</v>
+        <v>224</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -3053,34 +3071,34 @@
       <c r="C53" s="19"/>
       <c r="D53" s="19"/>
       <c r="E53" s="19" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G53" s="19" t="s">
-        <v>36</v>
+        <v>225</v>
+      </c>
+      <c r="G53" s="32" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="21" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="D54" s="21"/>
       <c r="E54" s="21" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="G54" s="21" t="s">
-        <v>48</v>
+        <v>224</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
@@ -3089,34 +3107,34 @@
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G55" s="19" t="s">
-        <v>124</v>
+        <v>225</v>
+      </c>
+      <c r="G55" s="32" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="21" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="21" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="G56" s="21" t="s">
-        <v>32</v>
+        <v>224</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -3139,33 +3157,33 @@
     <col min="4" max="4" width="27.109375" style="9" customWidth="1"/>
     <col min="5" max="5" width="27.109375" style="15" customWidth="1"/>
     <col min="6" max="6" width="29.77734375" customWidth="1"/>
-    <col min="7" max="7" width="29.77734375" style="49" customWidth="1"/>
+    <col min="7" max="7" width="29.77734375" style="48" customWidth="1"/>
     <col min="8" max="8" width="21" style="15" customWidth="1"/>
-    <col min="9" max="11" width="21" style="43" customWidth="1"/>
+    <col min="9" max="11" width="21" style="42" customWidth="1"/>
     <col min="12" max="12" width="18.77734375" customWidth="1"/>
     <col min="13" max="14" width="17.77734375" customWidth="1"/>
     <col min="15" max="15" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
     </row>
     <row r="2" spans="1:15" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3174,39 +3192,39 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
+        <v>314</v>
+      </c>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
     </row>
     <row r="3" spans="1:15" s="20" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>14</v>
@@ -3215,28 +3233,28 @@
         <v>15</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>19</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J3" s="19"/>
       <c r="K3" s="19"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:15" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>14</v>
@@ -3245,10 +3263,10 @@
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
       <c r="F4" s="16" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
@@ -3263,10 +3281,10 @@
       <c r="D5" s="19"/>
       <c r="E5" s="19"/>
       <c r="F5" s="32" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
@@ -3279,25 +3297,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -3309,25 +3327,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="I7" s="32"/>
       <c r="J7" s="32"/>
@@ -3339,22 +3357,22 @@
         <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -3367,26 +3385,26 @@
         <v>13</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="H9" s="32"/>
       <c r="I9" s="32" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
@@ -3397,26 +3415,26 @@
         <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -3424,25 +3442,25 @@
     </row>
     <row r="11" spans="1:15" s="20" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
@@ -3452,13 +3470,13 @@
     </row>
     <row r="12" spans="1:15" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -3470,21 +3488,21 @@
         <v>14</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="32" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
@@ -3496,21 +3514,21 @@
         <v>14</v>
       </c>
       <c r="K13" s="32" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="L13" s="32" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:15" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -3522,21 +3540,21 @@
         <v>14</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
@@ -3545,24 +3563,24 @@
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="K15" s="32" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="L15" s="32" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -3571,24 +3589,24 @@
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="20" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
@@ -3597,13 +3615,13 @@
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="19" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="L17" s="19" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -3656,30 +3674,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="24.88671875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="5" max="5" width="28" style="53" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" style="15" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3688,166 +3708,177 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>154</v>
+        <v>38</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="G2" s="20"/>
-    </row>
-    <row r="3" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="36"/>
-    </row>
-    <row r="4" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="E3" s="19"/>
+      <c r="F3" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="35"/>
+    </row>
+    <row r="4" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="F5" s="19"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="E5" s="19"/>
+      <c r="F5" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="F6" s="17"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F7" s="11"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="F8" s="17"/>
-    </row>
-    <row r="9" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="G8" s="17"/>
+    </row>
+    <row r="9" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="F9" s="19"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="F10" s="17"/>
+        <v>48</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="G10" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3868,19 +3899,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -3889,175 +3920,175 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="29" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="F6" s="30"/>
       <c r="G6" s="30" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H7" s="32"/>
     </row>
     <row r="8" spans="1:8" s="20" customFormat="1" ht="66" x14ac:dyDescent="0.3">
       <c r="A8" s="29" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="F8" s="29"/>
       <c r="G8" s="30" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H8" s="32"/>
     </row>
     <row r="9" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
       <c r="G9" s="32" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="29" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="D10" s="29"/>
       <c r="E10" s="29"/>
       <c r="F10" s="29"/>
       <c r="G10" s="30" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="H10" s="19"/>
     </row>
@@ -4084,19 +4115,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
       <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4105,13 +4136,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="G2" s="15"/>
     </row>
@@ -4120,13 +4151,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -4137,13 +4168,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -4157,13 +4188,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="20"/>
@@ -4173,13 +4204,13 @@
         <v>18</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -4190,13 +4221,13 @@
         <v>18</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -4207,13 +4238,13 @@
         <v>18</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -4224,16 +4255,16 @@
         <v>18</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="20"/>
@@ -4243,13 +4274,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -4266,10 +4297,10 @@
         <v>23</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="20"/>
@@ -4288,7 +4319,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F12" s="18"/>
       <c r="G12" s="20"/>
@@ -4298,16 +4329,16 @@
         <v>18</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>19</v>
@@ -4318,10 +4349,10 @@
         <v>21</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>20</v>
@@ -4334,10 +4365,10 @@
         <v>21</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>20</v>
@@ -4350,10 +4381,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>20</v>
@@ -4367,26 +4398,26 @@
         <v>21</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
@@ -4394,13 +4425,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -4432,20 +4463,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4454,30 +4485,30 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>376</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="2" t="s">
@@ -4491,88 +4522,88 @@
     </row>
     <row r="4" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H5" s="11"/>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="21" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
@@ -4580,162 +4611,162 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="H8" s="21"/>
     </row>
     <row r="9" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="D9" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="21" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="D10" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>119</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>139</v>
-      </c>
       <c r="G11" s="11" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="21" t="s">
         <v>99</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>121</v>
       </c>
       <c r="F12" s="21"/>
       <c r="G12" s="21" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H12" s="21"/>
     </row>
     <row r="13" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="D13" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H13" s="11"/>
     </row>
     <row r="14" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -4743,16 +4774,16 @@
     </row>
     <row r="15" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E15" s="32" t="s">
         <v>14</v>
@@ -4763,41 +4794,41 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" s="20" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="32" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -4805,19 +4836,19 @@
     </row>
     <row r="18" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -4825,19 +4856,19 @@
     </row>
     <row r="19" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -4845,19 +4876,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -4882,7 +4913,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" style="9" customWidth="1"/>
     <col min="3" max="3" width="39.5546875" style="15" customWidth="1"/>
     <col min="4" max="4" width="34.44140625" style="9" customWidth="1"/>
     <col min="5" max="5" width="34.44140625" style="15" customWidth="1"/>
@@ -4890,18 +4921,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -4910,460 +4941,460 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="H2" s="9"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>26</v>
+        <v>95</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>27</v>
+        <v>95</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>386</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E4" s="33"/>
       <c r="F4" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>28</v>
+        <v>95</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>387</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="22"/>
       <c r="F5" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>30</v>
+        <v>95</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>388</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="33"/>
       <c r="F6" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>32</v>
+        <v>95</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>390</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>33</v>
+        <v>95</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>34</v>
+        <v>95</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>392</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>35</v>
+        <v>95</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>36</v>
+        <v>95</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>394</v>
       </c>
       <c r="C12" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>290</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>313</v>
       </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>37</v>
+        <v>95</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>395</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>38</v>
+        <v>95</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="E14" s="33"/>
       <c r="F14" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>39</v>
+        <v>95</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>40</v>
+        <v>95</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>398</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E16" s="33"/>
       <c r="F16" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>41</v>
+        <v>95</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>399</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>42</v>
+        <v>95</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>43</v>
+        <v>95</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>401</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>44</v>
+        <v>95</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>402</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="E20" s="33"/>
       <c r="F20" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>45</v>
+        <v>95</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>403</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E21" s="34"/>
-      <c r="F21" s="42" t="s">
-        <v>313</v>
+      <c r="F21" s="41" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>46</v>
+        <v>95</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>404</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="E22" s="33"/>
       <c r="F22" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>47</v>
+        <v>95</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>405</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>48</v>
+        <v>95</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>406</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="E24" s="33"/>
       <c r="F24" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G24" s="9"/>
     </row>
     <row r="25" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>124</v>
+        <v>95</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>407</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G25" s="9"/>
     </row>
@@ -5430,27 +5461,27 @@
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="26.109375" customWidth="1"/>
-    <col min="5" max="7" width="26.109375" style="45" customWidth="1"/>
-    <col min="8" max="8" width="21" style="46" customWidth="1"/>
+    <col min="5" max="7" width="26.109375" style="44" customWidth="1"/>
+    <col min="8" max="8" width="21" style="45" customWidth="1"/>
     <col min="9" max="9" width="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
     </row>
     <row r="2" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -5459,283 +5490,283 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="H3" s="19"/>
       <c r="I3" s="19"/>
     </row>
     <row r="4" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="48" t="s">
-        <v>341</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>348</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>361</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>349</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>347</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
+      <c r="A4" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>325</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>326</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
     </row>
     <row r="5" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
     </row>
     <row r="6" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="48" t="s">
-        <v>341</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>363</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>129</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>358</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
+      <c r="A6" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>364</v>
-      </c>
       <c r="D7" s="19" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="48" t="s">
-        <v>341</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>352</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>365</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>350</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>347</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="48" t="s">
-        <v>246</v>
-      </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
+      <c r="A8" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>329</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>342</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>327</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="48" t="s">
-        <v>341</v>
-      </c>
-      <c r="B10" s="48" t="s">
-        <v>354</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>367</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>342</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
+      <c r="A10" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>319</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
     </row>
     <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="19"/>
     </row>
-    <row r="12" spans="1:9" s="51" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48" t="s">
-        <v>341</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>388</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>386</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>370</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>387</v>
-      </c>
-      <c r="F12" s="48" t="s">
+    <row r="12" spans="1:9" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>363</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>361</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>362</v>
+      </c>
+      <c r="F12" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
+      <c r="G12" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
     </row>
     <row r="13" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
@@ -5745,28 +5776,28 @@
         <v>14</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>278</v>
-      </c>
-      <c r="C14" s="48" t="s">
-        <v>276</v>
-      </c>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" s="48" t="s">
-        <v>373</v>
+      <c r="A14" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="47" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -5784,45 +5815,45 @@
       <c r="F16"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="36"/>
       <c r="E17"/>
       <c r="F17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="47"/>
+      <c r="A18" s="46"/>
       <c r="E18"/>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="47"/>
+      <c r="A19" s="46"/>
       <c r="E19"/>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="47"/>
-      <c r="C20" s="45"/>
+      <c r="A20" s="46"/>
+      <c r="C20" s="44"/>
       <c r="E20"/>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C21" s="45"/>
+      <c r="C21" s="44"/>
       <c r="E21"/>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C22" s="45"/>
+      <c r="C22" s="44"/>
       <c r="E22"/>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
       <c r="E23"/>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
       <c r="E24"/>
       <c r="F24"/>
     </row>
@@ -5837,32 +5868,32 @@
       <c r="H28" s="28"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
     </row>
     <row r="34" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
     </row>
     <row r="35" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5884,16 +5915,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -5902,18 +5933,18 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>14</v>
@@ -5921,13 +5952,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>14</v>
@@ -5935,13 +5966,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>14</v>
@@ -5949,65 +5980,65 @@
     </row>
     <row r="6" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C10" s="15"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D11" s="44"/>
+      <c r="D11" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
